--- a/Two Stage Deterministic equivalent/production_capacity_updated.xlsx
+++ b/Two Stage Deterministic equivalent/production_capacity_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Vaccine_Tender_Scheduling_Problem\Julia_Files\Github\Github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Two Stage Deterministic equivalent/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F91A28E-E3A4-4133-8CE8-00AB1748B441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{4F91A28E-E3A4-4133-8CE8-00AB1748B441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EF48A84-5BB7-401A-A202-1BED0F225B56}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{752E71BE-3FD4-4CCA-ABF0-6C5710D300B4}"/>
   </bookViews>
   <sheets>
     <sheet name="vaccine-producer list" sheetId="8" r:id="rId1"/>
@@ -2318,15 +2318,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3694F37-B2B5-4F9D-9ACD-67519624FADB}">
-  <dimension ref="A1:T54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="91.109375" customWidth="1"/>
-    <col min="2" max="18" width="15.6640625" customWidth="1"/>
-    <col min="20" max="20" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="91.140625" customWidth="1"/>
+    <col min="2" max="18" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="0" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
@@ -2415,8 +2416,12 @@
       <c r="R2" s="10"/>
       <c r="S2" s="34"/>
       <c r="T2" s="34"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U2">
+        <f>SUM(B2:T2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>92</v>
       </c>
@@ -2443,8 +2448,12 @@
       <c r="R3" s="10"/>
       <c r="S3" s="34"/>
       <c r="T3" s="34"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U3">
+        <f t="shared" ref="U3:U19" si="0">SUM(B3:T3)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>93</v>
       </c>
@@ -2471,8 +2480,12 @@
       <c r="R4" s="10"/>
       <c r="S4" s="34"/>
       <c r="T4" s="34"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>94</v>
       </c>
@@ -2501,8 +2514,12 @@
       <c r="R5" s="10"/>
       <c r="S5" s="34"/>
       <c r="T5" s="34"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>95</v>
       </c>
@@ -2531,8 +2548,12 @@
       <c r="R6" s="10"/>
       <c r="S6" s="34"/>
       <c r="T6" s="34"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>96</v>
       </c>
@@ -2561,8 +2582,12 @@
       <c r="R7" s="10"/>
       <c r="S7" s="34"/>
       <c r="T7" s="34"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>157</v>
       </c>
@@ -2595,8 +2620,12 @@
       <c r="R8" s="10"/>
       <c r="S8" s="34"/>
       <c r="T8" s="34"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>97</v>
       </c>
@@ -2623,8 +2652,12 @@
       <c r="R9" s="10"/>
       <c r="S9" s="34"/>
       <c r="T9" s="34"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>98</v>
       </c>
@@ -2649,8 +2682,12 @@
       <c r="R10" s="10"/>
       <c r="S10" s="34"/>
       <c r="T10" s="34"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>99</v>
       </c>
@@ -2683,8 +2720,12 @@
       <c r="R11" s="10"/>
       <c r="S11" s="34"/>
       <c r="T11" s="34"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>100</v>
       </c>
@@ -2709,8 +2750,12 @@
       <c r="R12" s="10"/>
       <c r="S12" s="34"/>
       <c r="T12" s="34"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>101</v>
       </c>
@@ -2741,8 +2786,12 @@
       <c r="R13" s="10"/>
       <c r="S13" s="34"/>
       <c r="T13" s="34"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U13">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>102</v>
       </c>
@@ -2781,8 +2830,12 @@
       <c r="R14" s="10"/>
       <c r="S14" s="34"/>
       <c r="T14" s="34"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>103</v>
       </c>
@@ -2813,8 +2866,12 @@
       <c r="T15" s="35">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U15">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>104</v>
       </c>
@@ -2841,8 +2898,12 @@
       <c r="R16" s="10"/>
       <c r="S16" s="34"/>
       <c r="T16" s="34"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>105</v>
       </c>
@@ -2871,8 +2932,12 @@
       </c>
       <c r="S17" s="34"/>
       <c r="T17" s="34"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>158</v>
       </c>
@@ -2901,8 +2966,12 @@
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U18">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>155</v>
       </c>
@@ -2931,8 +3000,12 @@
         <v>1</v>
       </c>
       <c r="T19" s="10"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2952,7 +3025,7 @@
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -2971,7 +3044,7 @@
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2990,7 +3063,7 @@
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -3009,7 +3082,7 @@
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -3028,7 +3101,7 @@
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -3047,7 +3120,7 @@
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -3066,7 +3139,7 @@
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -3085,7 +3158,7 @@
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -3104,7 +3177,7 @@
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -3123,7 +3196,7 @@
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -3142,7 +3215,7 @@
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -3161,7 +3234,7 @@
       <c r="Q31" s="13"/>
       <c r="R31" s="13"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -3180,7 +3253,7 @@
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -3199,7 +3272,7 @@
       <c r="Q33" s="13"/>
       <c r="R33" s="13"/>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -3218,7 +3291,7 @@
       <c r="Q34" s="13"/>
       <c r="R34" s="13"/>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -3237,7 +3310,7 @@
       <c r="Q35" s="13"/>
       <c r="R35" s="13"/>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -3256,7 +3329,7 @@
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -3275,7 +3348,7 @@
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -3294,7 +3367,7 @@
       <c r="Q38" s="13"/>
       <c r="R38" s="13"/>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -3313,7 +3386,7 @@
       <c r="Q39" s="13"/>
       <c r="R39" s="13"/>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -3332,7 +3405,7 @@
       <c r="Q40" s="13"/>
       <c r="R40" s="13"/>
     </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
@@ -3351,7 +3424,7 @@
       <c r="Q41" s="13"/>
       <c r="R41" s="13"/>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -3370,7 +3443,7 @@
       <c r="Q42" s="13"/>
       <c r="R42" s="13"/>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -3389,7 +3462,7 @@
       <c r="Q43" s="13"/>
       <c r="R43" s="13"/>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -3408,7 +3481,7 @@
       <c r="Q44" s="13"/>
       <c r="R44" s="13"/>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -3427,7 +3500,7 @@
       <c r="Q45" s="13"/>
       <c r="R45" s="13"/>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -3446,7 +3519,7 @@
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -3465,7 +3538,7 @@
       <c r="Q47" s="13"/>
       <c r="R47" s="13"/>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -3484,7 +3557,7 @@
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -3503,7 +3576,7 @@
       <c r="Q49" s="13"/>
       <c r="R49" s="13"/>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
       <c r="D50" s="13"/>
@@ -3522,7 +3595,7 @@
       <c r="Q50" s="13"/>
       <c r="R50" s="13"/>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
@@ -3541,7 +3614,7 @@
       <c r="Q51" s="13"/>
       <c r="R51" s="13"/>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
@@ -3560,7 +3633,7 @@
       <c r="Q52" s="13"/>
       <c r="R52" s="13"/>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -3579,7 +3652,7 @@
       <c r="Q53" s="13"/>
       <c r="R53" s="13"/>
     </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -3630,17 +3703,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7054496A-AF4B-4EC1-B368-49C550220A1C}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L301"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="94.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="94.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="16" style="2" customWidth="1"/>
     <col min="5" max="12" width="18" style="2" customWidth="1"/>
     <col min="13" max="13" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="2"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3678,7 +3751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
@@ -3696,7 +3769,7 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>12</v>
       </c>
@@ -3734,7 +3807,7 @@
         <v>26819200.996155463</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
         <v>12</v>
       </c>
@@ -3772,7 +3845,7 @@
         <v>56018232.597976193</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="43" t="s">
         <v>12</v>
       </c>
@@ -3810,7 +3883,7 @@
         <v>170565705.92964286</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="43" t="s">
         <v>12</v>
       </c>
@@ -3848,7 +3921,7 @@
         <v>79877180.657261893</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="43" t="s">
         <v>18</v>
       </c>
@@ -3878,7 +3951,7 @@
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="43" t="s">
         <v>18</v>
       </c>
@@ -3908,7 +3981,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="43" t="s">
         <v>18</v>
       </c>
@@ -3938,7 +4011,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
         <v>18</v>
       </c>
@@ -3968,7 +4041,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="43" t="s">
         <v>19</v>
       </c>
@@ -4006,7 +4079,7 @@
         <v>1403270410.0475006</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="43" t="s">
         <v>19</v>
       </c>
@@ -4044,7 +4117,7 @@
         <v>43232783.299999997</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="43" t="s">
         <v>19</v>
       </c>
@@ -4082,7 +4155,7 @@
         <v>789204932.27500033</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="43" t="s">
         <v>19</v>
       </c>
@@ -4120,7 +4193,7 @@
         <v>500814543.58749998</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -4138,7 +4211,7 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -4156,7 +4229,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="43" t="s">
         <v>22</v>
       </c>
@@ -4174,7 +4247,7 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="43" t="s">
         <v>22</v>
       </c>
@@ -4212,7 +4285,7 @@
         <v>12788293.736842105</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
         <v>22</v>
       </c>
@@ -4250,7 +4323,7 @@
         <v>863986.71500000008</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
         <v>22</v>
       </c>
@@ -4288,7 +4361,7 @@
         <v>5370201.9115789467</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
         <v>22</v>
       </c>
@@ -4326,7 +4399,7 @@
         <v>4313357.7878842624</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
         <v>23</v>
       </c>
@@ -4344,7 +4417,7 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
         <v>23</v>
       </c>
@@ -4382,7 +4455,7 @@
         <v>44326790.909789473</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
         <v>23</v>
       </c>
@@ -4400,7 +4473,7 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
         <v>23</v>
       </c>
@@ -4430,7 +4503,7 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="43" t="s">
         <v>23</v>
       </c>
@@ -4468,7 +4541,7 @@
         <v>430931.20894736843</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
@@ -4486,7 +4559,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="43" t="s">
         <v>25</v>
       </c>
@@ -4524,7 +4597,7 @@
         <v>24359.106315789475</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="43" t="s">
         <v>25</v>
       </c>
@@ -4554,7 +4627,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="43" t="s">
         <v>25</v>
       </c>
@@ -4580,7 +4653,7 @@
         <v>29653.105263157893</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>26</v>
       </c>
@@ -4618,7 +4691,7 @@
         <v>22700002.013999999</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>26</v>
       </c>
@@ -4644,7 +4717,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>26</v>
       </c>
@@ -4682,7 +4755,7 @@
         <v>9708542.1121710539</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>27</v>
       </c>
@@ -4720,7 +4793,7 @@
         <v>2385352.0408421056</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="s">
         <v>27</v>
       </c>
@@ -4750,7 +4823,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
         <v>27</v>
       </c>
@@ -4776,7 +4849,7 @@
         <v>6987.9032894736847</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>28</v>
       </c>
@@ -4814,7 +4887,7 @@
         <v>3753257.1406578948</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
         <v>28</v>
       </c>
@@ -4840,7 +4913,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="43" t="s">
         <v>29</v>
       </c>
@@ -4878,7 +4951,7 @@
         <v>17711618.430631582</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
         <v>29</v>
       </c>
@@ -4904,7 +4977,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="s">
         <v>29</v>
       </c>
@@ -4942,7 +5015,7 @@
         <v>8274488.3427631576</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="43" t="s">
         <v>30</v>
       </c>
@@ -4980,7 +5053,7 @@
         <v>12708293.497763159</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="s">
         <v>30</v>
       </c>
@@ -4998,7 +5071,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="43" t="s">
         <v>30</v>
       </c>
@@ -5036,7 +5109,7 @@
         <v>129709.70407894738</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
         <v>31</v>
       </c>
@@ -5054,7 +5127,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="43" t="s">
         <v>31</v>
       </c>
@@ -5092,7 +5165,7 @@
         <v>4366498.504999999</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="43" t="s">
         <v>31</v>
       </c>
@@ -5130,7 +5203,7 @@
         <v>924903.77499999991</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="43" t="s">
         <v>31</v>
       </c>
@@ -5168,7 +5241,7 @@
         <v>56671594.19749999</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="43" t="s">
         <v>31</v>
       </c>
@@ -5206,7 +5279,7 @@
         <v>28451376.886823118</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="43" t="s">
         <v>32</v>
       </c>
@@ -5224,7 +5297,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="43" t="s">
         <v>32</v>
       </c>
@@ -5242,7 +5315,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
         <v>32</v>
       </c>
@@ -5260,7 +5333,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="43" t="s">
         <v>32</v>
       </c>
@@ -5298,7 +5371,7 @@
         <v>1371371.7111111111</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="43" t="s">
         <v>33</v>
       </c>
@@ -5336,7 +5409,7 @@
         <v>4588112.7602708973</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="43" t="s">
         <v>33</v>
       </c>
@@ -5374,7 +5447,7 @@
         <v>68258991.188157901</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="43" t="s">
         <v>33</v>
       </c>
@@ -5412,7 +5485,7 @@
         <v>202310628.16776317</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
         <v>33</v>
       </c>
@@ -5450,7 +5523,7 @@
         <v>61534344.793815792</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
         <v>34</v>
       </c>
@@ -5488,7 +5561,7 @@
         <v>99151.439999999988</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="43" t="s">
         <v>34</v>
       </c>
@@ -5526,7 +5599,7 @@
         <v>3781590.8850000007</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="43" t="s">
         <v>34</v>
       </c>
@@ -5564,7 +5637,7 @@
         <v>2364272.5157894739</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
         <v>34</v>
       </c>
@@ -5584,7 +5657,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="43" t="s">
         <v>35</v>
       </c>
@@ -5622,7 +5695,7 @@
         <v>42709218.048947372</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="43" t="s">
         <v>35</v>
       </c>
@@ -5660,7 +5733,7 @@
         <v>585519.70234210533</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="43" t="s">
         <v>35</v>
       </c>
@@ -5698,7 +5771,7 @@
         <v>6391844.9436842091</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="43" t="s">
         <v>36</v>
       </c>
@@ -5716,7 +5789,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="43" t="s">
         <v>36</v>
       </c>
@@ -5754,7 +5827,7 @@
         <v>71135570.336828187</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="43" t="s">
         <v>36</v>
       </c>
@@ -5792,7 +5865,7 @@
         <v>8918362.7869736832</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
         <v>36</v>
       </c>
@@ -5830,7 +5903,7 @@
         <v>56037443.403815791</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="43" t="s">
         <v>36</v>
       </c>
@@ -5868,7 +5941,7 @@
         <v>26078721.471578948</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="43" t="s">
         <v>37</v>
       </c>
@@ -5886,7 +5959,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="43" t="s">
         <v>37</v>
       </c>
@@ -5924,7 +5997,7 @@
         <v>13285092.037631579</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="43" t="s">
         <v>37</v>
       </c>
@@ -5942,7 +6015,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="43" t="s">
         <v>37</v>
       </c>
@@ -5972,7 +6045,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="43" t="s">
         <v>37</v>
       </c>
@@ -6010,7 +6083,7 @@
         <v>7212690.1784210531</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="43" t="s">
         <v>38</v>
       </c>
@@ -6040,7 +6113,7 @@
         <v>3143161.6294736844</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="43" t="s">
         <v>38</v>
       </c>
@@ -6066,7 +6139,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>39</v>
       </c>
@@ -6104,7 +6177,7 @@
         <v>694846.97368421056</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="43" t="s">
         <v>40</v>
       </c>
@@ -6142,7 +6215,7 @@
         <v>31169164.653893046</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
         <v>40</v>
       </c>
@@ -6180,7 +6253,7 @@
         <v>9024207.2250826061</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
         <v>40</v>
       </c>
@@ -6218,7 +6291,7 @@
         <v>26014337.772836529</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="43" t="s">
         <v>40</v>
       </c>
@@ -6256,7 +6329,7 @@
         <v>21218834.523721006</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="43" t="s">
         <v>41</v>
       </c>
@@ -6294,7 +6367,7 @@
         <v>24485113.215146199</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="43" t="s">
         <v>41</v>
       </c>
@@ -6332,7 +6405,7 @@
         <v>42986086.185204685</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="43" t="s">
         <v>41</v>
       </c>
@@ -6370,7 +6443,7 @@
         <v>89969889.638869569</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
         <v>41</v>
       </c>
@@ -6408,7 +6481,7 @@
         <v>43092807.72445029</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
         <v>42</v>
       </c>
@@ -6446,7 +6519,7 @@
         <v>26223826.190433443</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="43" t="s">
         <v>42</v>
       </c>
@@ -6464,7 +6537,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="43" t="s">
         <v>42</v>
       </c>
@@ -6502,7 +6575,7 @@
         <v>38913109.206510134</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="43" t="s">
         <v>42</v>
       </c>
@@ -6540,7 +6613,7 @@
         <v>8318128.2670879252</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="44" t="s">
         <v>43</v>
       </c>
@@ -6558,7 +6631,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="45" t="s">
         <v>43</v>
       </c>
@@ -6596,7 +6669,7 @@
         <v>593298.1894736843</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="45" t="s">
         <v>43</v>
       </c>
@@ -6634,7 +6707,7 @@
         <v>882693.01642857143</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="45" t="s">
         <v>43</v>
       </c>
@@ -6672,7 +6745,7 @@
         <v>68866.200000000012</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="46" t="s">
         <v>43</v>
       </c>
@@ -6710,7 +6783,7 @@
         <v>9727462.9341666661</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="43" t="s">
         <v>44</v>
       </c>
@@ -6748,7 +6821,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="43" t="s">
         <v>44</v>
       </c>
@@ -6786,7 +6859,7 @@
         <v>16995032.578833334</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="43" t="s">
         <v>44</v>
       </c>
@@ -6824,7 +6897,7 @@
         <v>22529845.132500004</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="43" t="s">
         <v>45</v>
       </c>
@@ -6854,7 +6927,7 @@
         <v>11652763.552941177</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="43" t="s">
         <v>45</v>
       </c>
@@ -6872,7 +6945,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="43" t="s">
         <v>45</v>
       </c>
@@ -6898,7 +6971,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="43" t="s">
         <v>46</v>
       </c>
@@ -6936,7 +7009,7 @@
         <v>3129137.4496973683</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="43" t="s">
         <v>46</v>
       </c>
@@ -6954,7 +7027,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="43" t="s">
         <v>46</v>
       </c>
@@ -6980,7 +7053,7 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="43" t="s">
         <v>47</v>
       </c>
@@ -7010,7 +7083,7 @@
         <v>19439134.578947369</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="43" t="s">
         <v>47</v>
       </c>
@@ -7038,7 +7111,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="43" t="s">
         <v>47</v>
       </c>
@@ -7074,7 +7147,7 @@
         <v>12278482.1775</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="43" t="s">
         <v>48</v>
       </c>
@@ -7112,7 +7185,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="43" t="s">
         <v>48</v>
       </c>
@@ -7150,7 +7223,7 @@
         <v>428081.60342105263</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="43" t="s">
         <v>48</v>
       </c>
@@ -7168,7 +7241,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="43" t="s">
         <v>49</v>
       </c>
@@ -7206,7 +7279,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="43" t="s">
         <v>49</v>
       </c>
@@ -7244,7 +7317,7 @@
         <v>15938780.685739476</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="43" t="s">
         <v>49</v>
       </c>
@@ -7280,7 +7353,7 @@
         <v>7463.7629999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="43" t="s">
         <v>49</v>
       </c>
@@ -7318,7 +7391,7 @@
         <v>6024488.8079210529</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="43" t="s">
         <v>50</v>
       </c>
@@ -7356,7 +7429,7 @@
         <v>540000</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="43" t="s">
         <v>50</v>
       </c>
@@ -7394,7 +7467,7 @@
         <v>3357564.5291447369</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="43" t="s">
         <v>50</v>
       </c>
@@ -7432,7 +7505,7 @@
         <v>277375.88714868418</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="43" t="s">
         <v>50</v>
       </c>
@@ -7470,7 +7543,7 @@
         <v>48463.652665350877</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="43" t="s">
         <v>50</v>
       </c>
@@ -7506,7 +7579,7 @@
         <v>962589.57300000009</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>51</v>
       </c>
@@ -7544,7 +7617,7 @@
         <v>4199871.1182460524</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="43" t="s">
         <v>52</v>
       </c>
@@ -7562,7 +7635,7 @@
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="43" t="s">
         <v>52</v>
       </c>
@@ -7594,7 +7667,7 @@
         <v>8001.5255263157915</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="43" t="s">
         <v>52</v>
       </c>
@@ -7632,7 +7705,7 @@
         <v>196251.34736842106</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="43" t="s">
         <v>53</v>
       </c>
@@ -7670,7 +7743,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="43" t="s">
         <v>53</v>
       </c>
@@ -7708,7 +7781,7 @@
         <v>3969424.3796421057</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="43" t="s">
         <v>53</v>
       </c>
@@ -7746,7 +7819,7 @@
         <v>8895367.3138157893</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="43" t="s">
         <v>54</v>
       </c>
@@ -7764,7 +7837,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="43" t="s">
         <v>54</v>
       </c>
@@ -7782,7 +7855,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="43" t="s">
         <v>54</v>
       </c>
@@ -7800,7 +7873,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="43" t="s">
         <v>54</v>
       </c>
@@ -7820,7 +7893,7 @@
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="43" t="s">
         <v>55</v>
       </c>
@@ -7838,7 +7911,7 @@
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="43" t="s">
         <v>55</v>
       </c>
@@ -7876,7 +7949,7 @@
         <v>44666553.82686425</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="43" t="s">
         <v>55</v>
       </c>
@@ -7914,7 +7987,7 @@
         <v>2148068.0935714287</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="43" t="s">
         <v>55</v>
       </c>
@@ -7952,7 +8025,7 @@
         <v>10829590.64130117</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="43" t="s">
         <v>55</v>
       </c>
@@ -7990,7 +8063,7 @@
         <v>53816727.563368849</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="43" t="s">
         <v>56</v>
       </c>
@@ -8028,7 +8101,7 @@
         <v>5366204.9252105262</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="43" t="s">
         <v>56</v>
       </c>
@@ -8066,7 +8139,7 @@
         <v>1918456.0949999997</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="43" t="s">
         <v>57</v>
       </c>
@@ -8104,7 +8177,7 @@
         <v>2456094.4891353385</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="43" t="s">
         <v>57</v>
       </c>
@@ -8142,7 +8215,7 @@
         <v>84871745.658650786</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="43" t="s">
         <v>57</v>
       </c>
@@ -8180,7 +8253,7 @@
         <v>228007209.74936509</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="43" t="s">
         <v>57</v>
       </c>
@@ -8218,7 +8291,7 @@
         <v>32273220.97396826</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>58</v>
       </c>
@@ -8256,7 +8329,7 @@
         <v>1012182.5810526316</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="43" t="s">
         <v>59</v>
       </c>
@@ -8294,7 +8367,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="43" t="s">
         <v>59</v>
       </c>
@@ -8332,7 +8405,7 @@
         <v>19377207.360228568</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="43" t="s">
         <v>59</v>
       </c>
@@ -8370,7 +8443,7 @@
         <v>123225959.44543454</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="43" t="s">
         <v>59</v>
       </c>
@@ -8398,7 +8471,7 @@
         <v>9816494.2557882406</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="43" t="s">
         <v>60</v>
       </c>
@@ -8436,7 +8509,7 @@
         <v>85488520.6669323</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="43" t="s">
         <v>60</v>
       </c>
@@ -8474,7 +8547,7 @@
         <v>57292565.508875743</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="43" t="s">
         <v>60</v>
       </c>
@@ -8512,7 +8585,7 @@
         <v>162941685.62800577</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="43" t="s">
         <v>60</v>
       </c>
@@ -8550,7 +8623,7 @@
         <v>66591452.998300254</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="43" t="s">
         <v>61</v>
       </c>
@@ -8588,7 +8661,7 @@
         <v>6418700.4964842089</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="43" t="s">
         <v>61</v>
       </c>
@@ -8626,7 +8699,7 @@
         <v>657.72019736842117</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="43" t="s">
         <v>61</v>
       </c>
@@ -8664,7 +8737,7 @@
         <v>38980.994268421055</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="43" t="s">
         <v>62</v>
       </c>
@@ -8702,7 +8775,7 @@
         <v>57668115.752105266</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="43" t="s">
         <v>62</v>
       </c>
@@ -8740,7 +8813,7 @@
         <v>48207996.665438592</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="43" t="s">
         <v>62</v>
       </c>
@@ -8778,7 +8851,7 @@
         <v>163594841.15653506</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="43" t="s">
         <v>62</v>
       </c>
@@ -8816,7 +8889,7 @@
         <v>51145121.535921052</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="43" t="s">
         <v>63</v>
       </c>
@@ -8842,7 +8915,7 @@
         <v>1140116.518780523</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="43" t="s">
         <v>63</v>
       </c>
@@ -8868,7 +8941,7 @@
         <v>3095533.6346984911</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="43" t="s">
         <v>63</v>
       </c>
@@ -8896,7 +8969,7 @@
         <v>24073104.668296658</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="43" t="s">
         <v>63</v>
       </c>
@@ -8924,7 +8997,7 @@
         <v>8249515.7360912031</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="43" t="s">
         <v>64</v>
       </c>
@@ -8942,7 +9015,7 @@
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="43" t="s">
         <v>64</v>
       </c>
@@ -8960,7 +9033,7 @@
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="43" t="s">
         <v>64</v>
       </c>
@@ -8980,7 +9053,7 @@
       <c r="K163" s="6"/>
       <c r="L163" s="6"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="43" t="s">
         <v>65</v>
       </c>
@@ -9008,7 +9081,7 @@
         <v>524620.18888888881</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="43" t="s">
         <v>65</v>
       </c>
@@ -9046,7 +9119,7 @@
         <v>11686619.239444446</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="43" t="s">
         <v>65</v>
       </c>
@@ -9084,7 +9157,7 @@
         <v>67230835.707277775</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="43" t="s">
         <v>65</v>
       </c>
@@ -9122,7 +9195,7 @@
         <v>8927850.3513888884</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="43" t="s">
         <v>66</v>
       </c>
@@ -9140,7 +9213,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="43" t="s">
         <v>66</v>
       </c>
@@ -9178,7 +9251,7 @@
         <v>11586096.10842105</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="43" t="s">
         <v>66</v>
       </c>
@@ -9216,7 +9289,7 @@
         <v>61286058.379432946</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="43" t="s">
         <v>66</v>
       </c>
@@ -9254,7 +9327,7 @@
         <v>198326735.48209769</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="43" t="s">
         <v>66</v>
       </c>
@@ -9292,7 +9365,7 @@
         <v>74368544.324421823</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="43" t="s">
         <v>67</v>
       </c>
@@ -9330,7 +9403,7 @@
         <v>37434.968421052632</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="43" t="s">
         <v>67</v>
       </c>
@@ -9348,7 +9421,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="43" t="s">
         <v>67</v>
       </c>
@@ -9366,7 +9439,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="43" t="s">
         <v>68</v>
       </c>
@@ -9404,7 +9477,7 @@
         <v>14085732.501447368</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="43" t="s">
         <v>68</v>
       </c>
@@ -9436,7 +9509,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="43" t="s">
         <v>68</v>
       </c>
@@ -9474,7 +9547,7 @@
         <v>2658726.6143421056</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="43" t="s">
         <v>69</v>
       </c>
@@ -9512,7 +9585,7 @@
         <v>5274066.9230263159</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="43" t="s">
         <v>69</v>
       </c>
@@ -9538,7 +9611,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="43" t="s">
         <v>69</v>
       </c>
@@ -9576,7 +9649,7 @@
         <v>109338.78881578946</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="43" t="s">
         <v>70</v>
       </c>
@@ -9594,7 +9667,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="43" t="s">
         <v>70</v>
       </c>
@@ -9612,7 +9685,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="43" t="s">
         <v>70</v>
       </c>
@@ -9630,7 +9703,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="43" t="s">
         <v>70</v>
       </c>
@@ -9648,7 +9721,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="43" t="s">
         <v>70</v>
       </c>
@@ -9666,7 +9739,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="43" t="s">
         <v>71</v>
       </c>
@@ -9684,7 +9757,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="43" t="s">
         <v>71</v>
       </c>
@@ -9722,7 +9795,7 @@
         <v>1602020.15372807</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="43" t="s">
         <v>71</v>
       </c>
@@ -9760,7 +9833,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="43" t="s">
         <v>71</v>
       </c>
@@ -9786,7 +9859,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="43" t="s">
         <v>71</v>
       </c>
@@ -9824,7 +9897,7 @@
         <v>8435990.8228508774</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="43" t="s">
         <v>72</v>
       </c>
@@ -9842,7 +9915,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="43" t="s">
         <v>72</v>
       </c>
@@ -9880,7 +9953,7 @@
         <v>41053.861588892236</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="43" t="s">
         <v>72</v>
       </c>
@@ -9910,7 +9983,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="43" t="s">
         <v>72</v>
       </c>
@@ -9948,7 +10021,7 @@
         <v>361138.98097679514</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="43" t="s">
         <v>73</v>
       </c>
@@ -9986,7 +10059,7 @@
         <v>21801576.347789474</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="43" t="s">
         <v>73</v>
       </c>
@@ -10004,7 +10077,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="43" t="s">
         <v>73</v>
       </c>
@@ -10042,7 +10115,7 @@
         <v>4773371.973289473</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="43" t="s">
         <v>74</v>
       </c>
@@ -10080,7 +10153,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="43" t="s">
         <v>74</v>
       </c>
@@ -10118,7 +10191,7 @@
         <v>95686.964999999997</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="43" t="s">
         <v>74</v>
       </c>
@@ -10156,7 +10229,7 @@
         <v>19427327.223125003</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="43" t="s">
         <v>74</v>
       </c>
@@ -10194,7 +10267,7 @@
         <v>28291617.551274512</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="43" t="s">
         <v>74</v>
       </c>
@@ -10232,7 +10305,7 @@
         <v>21470697.767319441</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C204" s="8"/>
       <c r="D204" s="8"/>
       <c r="E204" s="8"/>
@@ -10244,7 +10317,7 @@
       <c r="K204" s="8"/>
       <c r="L204" s="8"/>
     </row>
-    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
       <c r="E205" s="8"/>
@@ -10256,7 +10329,7 @@
       <c r="K205" s="8"/>
       <c r="L205" s="8"/>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C206" s="8"/>
       <c r="D206" s="8"/>
       <c r="E206" s="8"/>
@@ -10268,7 +10341,7 @@
       <c r="K206" s="8"/>
       <c r="L206" s="8"/>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>43</v>
       </c>
@@ -10316,7 +10389,7 @@
         <v>22913488.673833333</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>57</v>
       </c>
@@ -10364,7 +10437,7 @@
         <v>312878955.40801585</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>55</v>
       </c>
@@ -10412,7 +10485,7 @@
         <v>12977658.734872598</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>71</v>
       </c>
@@ -10460,7 +10533,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>66</v>
       </c>
@@ -10508,7 +10581,7 @@
         <v>259612793.86153063</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>108</v>
       </c>
@@ -10556,7 +10629,7 @@
         <v>6234188.6265789466</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>109</v>
       </c>
@@ -10604,7 +10677,7 @@
         <v>57596497.972499989</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>98</v>
       </c>
@@ -10652,7 +10725,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>99</v>
       </c>
@@ -10700,7 +10773,7 @@
         <v>270569619.35592109</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="16" t="s">
         <v>100</v>
       </c>
@@ -10748,7 +10821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>101</v>
       </c>
@@ -10796,7 +10869,7 @@
         <v>132955975.82407425</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>102</v>
       </c>
@@ -10844,7 +10917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>103</v>
       </c>
@@ -10892,7 +10965,7 @@
         <v>35038544.997919135</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>104</v>
       </c>
@@ -10940,7 +11013,7 @@
         <v>64955806.190789476</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>105</v>
       </c>
@@ -10988,7 +11061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>62</v>
       </c>
@@ -11036,7 +11109,7 @@
         <v>211802837.82197365</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>60</v>
       </c>
@@ -11084,10 +11157,10 @@
         <v>220234251.13688153</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C224" s="8"/>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>113</v>
       </c>
@@ -11100,7 +11173,7 @@
       <c r="F225" s="8"/>
       <c r="G225" s="8"/>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>114</v>
       </c>
@@ -11109,7 +11182,7 @@
       </c>
       <c r="C226" s="8"/>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>106</v>
       </c>
@@ -11117,14 +11190,14 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H228" s="15"/>
       <c r="I228" s="15"/>
       <c r="J228" s="15"/>
       <c r="K228" s="15"/>
       <c r="L228" s="15"/>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B229" s="2" t="s">
         <v>115</v>
       </c>
@@ -11134,7 +11207,7 @@
       <c r="K229" s="27"/>
       <c r="L229" s="27"/>
     </row>
-    <row r="230" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="18" t="s">
         <v>43</v>
       </c>
@@ -11179,7 +11252,7 @@
         <v>20622139.806450002</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>75</v>
       </c>
@@ -11227,7 +11300,7 @@
         <v>16872659.841640912</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>118</v>
       </c>
@@ -11275,7 +11348,7 @@
         <v>3749479.9648090904</v>
       </c>
     </row>
-    <row r="233" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="18" t="s">
         <v>57</v>
       </c>
@@ -11320,7 +11393,7 @@
         <v>281591059.86721426</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>75</v>
       </c>
@@ -11368,7 +11441,7 @@
         <v>203910767.49005172</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>119</v>
       </c>
@@ -11416,7 +11489,7 @@
         <v>77680292.377162561</v>
       </c>
     </row>
-    <row r="236" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="18" t="s">
         <v>55</v>
       </c>
@@ -11461,7 +11534,7 @@
         <v>11679892.861385338</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>116</v>
       </c>
@@ -11509,7 +11582,7 @@
         <v>3412103.5325395376</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>117</v>
       </c>
@@ -11557,7 +11630,7 @@
         <v>8267789.3288458008</v>
       </c>
     </row>
-    <row r="239" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="18" t="s">
         <v>71</v>
       </c>
@@ -11602,7 +11675,7 @@
         <v>3089470.1716666664</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>75</v>
       </c>
@@ -11650,7 +11723,7 @@
         <v>2289842.5978235295</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>118</v>
       </c>
@@ -11698,7 +11771,7 @@
         <v>508853.91062745103</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>81</v>
       </c>
@@ -11746,7 +11819,7 @@
         <v>290773.66321568622</v>
       </c>
     </row>
-    <row r="243" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="18" t="s">
         <v>66</v>
       </c>
@@ -11791,7 +11864,7 @@
         <v>259612793.86153063</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>75</v>
       </c>
@@ -11839,7 +11912,7 @@
         <v>192418894.27384037</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>118</v>
       </c>
@@ -11887,7 +11960,7 @@
         <v>42759754.283075638</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>81</v>
       </c>
@@ -11935,7 +12008,7 @@
         <v>24434145.304614648</v>
       </c>
     </row>
-    <row r="247" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="18" t="s">
         <v>108</v>
       </c>
@@ -11980,7 +12053,7 @@
         <v>6857607.4892368419</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>75</v>
       </c>
@@ -12028,7 +12101,7 @@
         <v>5082697.3155520121</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>118</v>
       </c>
@@ -12076,7 +12149,7 @@
         <v>1129488.2923448917</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>81</v>
       </c>
@@ -12124,7 +12197,7 @@
         <v>645421.88133993803</v>
       </c>
     </row>
-    <row r="251" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="18" t="s">
         <v>109</v>
       </c>
@@ -12169,7 +12242,7 @@
         <v>63356147.769749992</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>75</v>
       </c>
@@ -12217,7 +12290,7 @@
         <v>45878589.764301717</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>119</v>
       </c>
@@ -12265,7 +12338,7 @@
         <v>17477558.005448274</v>
       </c>
     </row>
-    <row r="254" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="18" t="s">
         <v>98</v>
       </c>
@@ -12310,7 +12383,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>75</v>
       </c>
@@ -12358,7 +12431,7 @@
         <v>6145863.4007894751</v>
       </c>
     </row>
-    <row r="256" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="18" t="s">
         <v>99</v>
       </c>
@@ -12403,7 +12476,7 @@
         <v>297626581.2915132</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>75</v>
       </c>
@@ -12451,7 +12524,7 @@
         <v>165933403.72889677</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>118</v>
       </c>
@@ -12499,7 +12572,7 @@
         <v>36874089.717532612</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>119</v>
       </c>
@@ -12547,7 +12620,7 @@
         <v>63212725.230055898</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>82</v>
       </c>
@@ -12595,7 +12668,7 @@
         <v>21070908.410018638</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>83</v>
       </c>
@@ -12643,12 +12716,12 @@
         <v>10535454.205009319</v>
       </c>
     </row>
-    <row r="262" spans="1:12" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" s="21" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="23" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="263" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="18" t="s">
         <v>101</v>
       </c>
@@ -12693,7 +12766,7 @@
         <v>146251573.40648168</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>82</v>
       </c>
@@ -12741,7 +12814,7 @@
         <v>53182390.329629704</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>84</v>
       </c>
@@ -12789,7 +12862,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>85</v>
       </c>
@@ -12837,7 +12910,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>86</v>
       </c>
@@ -12885,7 +12958,7 @@
         <v>59830189.120833419</v>
       </c>
     </row>
-    <row r="268" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="18" t="s">
         <v>102</v>
       </c>
@@ -12930,7 +13003,7 @@
         <v>404502055.98924994</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>75</v>
       </c>
@@ -12978,7 +13051,7 @@
         <v>172186685.99542397</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" s="22" t="s">
         <v>76</v>
       </c>
@@ -13026,7 +13099,7 @@
         <v>38263707.998983108</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>77</v>
       </c>
@@ -13074,7 +13147,7 @@
         <v>71061171.998111486</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>80</v>
       </c>
@@ -13122,7 +13195,7 @@
         <v>68328049.998184115</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>83</v>
       </c>
@@ -13170,7 +13243,7 @@
         <v>10932487.999709459</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>87</v>
       </c>
@@ -13218,7 +13291,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>88</v>
       </c>
@@ -13266,7 +13339,7 @@
         <v>27331219.999273647</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>89</v>
       </c>
@@ -13314,7 +13387,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="277" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="18" t="s">
         <v>103</v>
       </c>
@@ -13359,7 +13432,7 @@
         <v>31534690.498127222</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>77</v>
       </c>
@@ -13407,7 +13480,7 @@
         <v>24845513.725797206</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>79</v>
       </c>
@@ -13455,7 +13528,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>90</v>
       </c>
@@ -13503,7 +13576,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" s="28" t="s">
         <v>154</v>
       </c>
@@ -13546,7 +13619,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="282" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="18" t="s">
         <v>104</v>
       </c>
@@ -13591,7 +13664,7 @@
         <v>71451386.809868425</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>75</v>
       </c>
@@ -13639,7 +13712,7 @@
         <v>63400526.324249454</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>82</v>
       </c>
@@ -13687,7 +13760,7 @@
         <v>8050860.485618975</v>
       </c>
     </row>
-    <row r="285" spans="1:12" s="19" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:12" s="19" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="18" t="s">
         <v>105</v>
       </c>
@@ -13732,7 +13805,7 @@
         <v>3954.38333881579</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>75</v>
       </c>
@@ -13780,7 +13853,7 @@
         <v>2737.650003795547</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>80</v>
       </c>
@@ -13828,7 +13901,7 @@
         <v>1086.3690491252169</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>91</v>
       </c>
@@ -13876,7 +13949,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="289" spans="1:12" s="30" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:12" s="30" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="29" t="s">
         <v>62</v>
       </c>
@@ -13921,7 +13994,7 @@
         <v>190622554.0397763</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>75</v>
       </c>
@@ -13969,7 +14042,7 @@
         <v>121305261.66167584</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>88</v>
       </c>
@@ -14017,7 +14090,7 @@
         <v>13932545.477990292</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>77</v>
       </c>
@@ -14065,7 +14138,7 @@
         <v>50062488.939739235</v>
       </c>
     </row>
-    <row r="293" spans="1:12" s="30" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:12" s="30" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="29" t="s">
         <v>155</v>
       </c>
@@ -14110,7 +14183,7 @@
         <v>242257676.2505697</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>75</v>
       </c>
@@ -14158,7 +14231,7 @@
         <v>165893843.51941183</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>156</v>
       </c>
@@ -14206,7 +14279,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>77</v>
       </c>
@@ -14254,7 +14327,7 @@
         <v>68464125.896900132</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H301" s="16"/>
       <c r="I301" s="16"/>
       <c r="J301" s="16"/>
@@ -14291,16 +14364,36 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="52">
-    <mergeCell ref="A187:A191"/>
-    <mergeCell ref="A192:A195"/>
-    <mergeCell ref="A196:A198"/>
-    <mergeCell ref="A199:A203"/>
-    <mergeCell ref="A164:A167"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A186"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A70:A74"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A69"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="A161:A163"/>
     <mergeCell ref="A120:A122"/>
     <mergeCell ref="A123:A125"/>
@@ -14313,36 +14406,16 @@
     <mergeCell ref="A150:A152"/>
     <mergeCell ref="A153:A156"/>
     <mergeCell ref="A157:A160"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A70:A74"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A69"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A187:A191"/>
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="A196:A198"/>
+    <mergeCell ref="A199:A203"/>
+    <mergeCell ref="A164:A167"/>
+    <mergeCell ref="A168:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A186"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -14353,15 +14426,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55228539-2602-4D9E-BF99-AB1A3FA50A1F}">
   <dimension ref="A1:W63"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>120</v>
       </c>
@@ -14396,7 +14469,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -14431,7 +14504,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>140</v>
       </c>
@@ -14499,7 +14572,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>140</v>
       </c>
@@ -14567,7 +14640,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>140</v>
       </c>
@@ -14635,7 +14708,7 @@
         <v>25370340.849170271</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -14703,7 +14776,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>142</v>
       </c>
@@ -14771,7 +14844,7 @@
         <v>41263765.477263942</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>142</v>
       </c>
@@ -14839,7 +14912,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>143</v>
       </c>
@@ -14907,7 +14980,7 @@
         <v>158370575.61266673</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>144</v>
       </c>
@@ -14975,7 +15048,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>144</v>
       </c>
@@ -15043,7 +15116,7 @@
         <v>217845404.09308761</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>144</v>
       </c>
@@ -15111,7 +15184,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>145</v>
       </c>
@@ -15179,7 +15252,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>116</v>
       </c>
@@ -15247,7 +15320,7 @@
         <v>82304159.225267321</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>116</v>
       </c>
@@ -15315,7 +15388,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>116</v>
       </c>
@@ -15383,7 +15456,7 @@
         <v>21467942.204718776</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>116</v>
       </c>
@@ -15451,7 +15524,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>116</v>
       </c>
@@ -15519,7 +15592,7 @@
         <v>123285374.16737279</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>146</v>
       </c>
@@ -15587,7 +15660,7 @@
         <v>128159325.48806667</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>154</v>
       </c>
@@ -15655,7 +15728,7 @@
         <v>1169589562.8925073</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>147</v>
       </c>
@@ -15723,7 +15796,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>147</v>
       </c>
@@ -15791,7 +15864,7 @@
         <v>2032838786.6183393</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>147</v>
       </c>
@@ -15826,7 +15899,7 @@
         <v>8050860.485618975</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>148</v>
       </c>
@@ -15861,7 +15934,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>149</v>
       </c>
@@ -15929,7 +16002,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>149</v>
       </c>
@@ -15997,7 +16070,7 @@
         <v>19943396.373611137</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>156</v>
       </c>
@@ -16065,7 +16138,7 @@
         <v>25370340.849170271</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>150</v>
       </c>
@@ -16133,7 +16206,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>150</v>
       </c>
@@ -16201,7 +16274,7 @@
         <v>41263765.477263942</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>150</v>
       </c>
@@ -16269,7 +16342,7 @@
         <v>13295597.582407426</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>150</v>
       </c>
@@ -16337,7 +16410,7 @@
         <v>158370575.61266673</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>150</v>
       </c>
@@ -16405,7 +16478,7 @@
         <v>130.36428589502603</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
         <v>150</v>
       </c>
@@ -16473,7 +16546,7 @@
         <v>217845404.09308761</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>151</v>
       </c>
@@ -16541,7 +16614,7 @@
         <v>8199365.9997820929</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -16609,7 +16682,7 @@
         <v>955596.68176143104</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>151</v>
       </c>
@@ -16677,7 +16750,7 @@
         <v>82304159.225267321</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>152</v>
       </c>
@@ -16745,7 +16818,7 @@
         <v>5733580.0905685853</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>152</v>
       </c>
@@ -16813,7 +16886,7 @@
         <v>21467942.204718776</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>152</v>
       </c>
@@ -16881,7 +16954,7 @@
         <v>7899706.834257707</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>152</v>
       </c>
@@ -16949,7 +17022,7 @@
         <v>123285374.16737279</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>152</v>
       </c>
@@ -17017,7 +17090,7 @@
         <v>128159325.48806667</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>152</v>
       </c>
@@ -17085,7 +17158,7 @@
         <v>1169589562.8925073</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>152</v>
       </c>
@@ -17153,7 +17226,7 @@
         <v>955596.68176143093</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>152</v>
       </c>
@@ -17221,7 +17294,7 @@
         <v>2032838786.6183393</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>152</v>
       </c>
@@ -17286,7 +17359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>152</v>
       </c>
@@ -17364,7 +17437,7 @@
         <v>19900000</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>152</v>
       </c>
@@ -17442,7 +17515,7 @@
         <v>25400000</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>152</v>
       </c>
@@ -17520,7 +17593,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>152</v>
       </c>
@@ -17598,7 +17671,7 @@
         <v>41300000</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>152</v>
       </c>
@@ -17676,7 +17749,7 @@
         <v>13300000</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>153</v>
       </c>
@@ -17754,7 +17827,7 @@
         <v>158400000</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M52" t="s">
         <v>145</v>
       </c>
@@ -17799,7 +17872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M53" t="s">
         <v>116</v>
       </c>
@@ -17844,7 +17917,7 @@
         <v>217800000</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M54" t="s">
         <v>146</v>
       </c>
@@ -17889,7 +17962,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M55" t="s">
         <v>154</v>
       </c>
@@ -17934,7 +18007,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M56" t="s">
         <v>147</v>
       </c>
@@ -17979,7 +18052,7 @@
         <v>82300000</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M57" t="s">
         <v>148</v>
       </c>
@@ -18024,7 +18097,7 @@
         <v>5700000</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M58" t="s">
         <v>149</v>
       </c>
@@ -18069,7 +18142,7 @@
         <v>21500000</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M59" t="s">
         <v>156</v>
       </c>
@@ -18114,7 +18187,7 @@
         <v>7900000</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M60" t="s">
         <v>150</v>
       </c>
@@ -18159,7 +18232,7 @@
         <v>123300000</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M61" t="s">
         <v>151</v>
       </c>
@@ -18204,7 +18277,7 @@
         <v>128200000</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M62" t="s">
         <v>152</v>
       </c>
@@ -18249,7 +18322,7 @@
         <v>1169600000</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M63" t="s">
         <v>153</v>
       </c>
@@ -18303,13 +18376,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{770C77AF-CB50-4854-8654-5465FF2CEF2B}">
   <dimension ref="B2:T19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
         <v>84</v>
       </c>
@@ -18365,7 +18438,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="26" t="s">
         <v>81</v>
       </c>
@@ -18437,7 +18510,7 @@
         <v>"Xiamen_Innovax",</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B4" s="26" t="s">
         <v>87</v>
       </c>
@@ -18449,7 +18522,7 @@
         <v>"AJ_Vaccines","BB_NCIPD","Beijing_Institute","Bharat_Biotech","Bilthoven","Biological_E","Centro_de","GSK","Haffkine_Bio","LG_Chem","Merck_Sharp","Panacea_Biotec","PT_Bio","Sanofi_Pasteur","Serum_Institute","Xiamen_Innovax",</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>88</v>
       </c>
@@ -18457,7 +18530,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6" s="26" t="s">
         <v>85</v>
       </c>
@@ -18465,7 +18538,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="26" t="s">
         <v>119</v>
       </c>
@@ -18473,7 +18546,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B8" s="26" t="s">
         <v>91</v>
       </c>
@@ -18481,7 +18554,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" s="26" t="s">
         <v>77</v>
       </c>
@@ -18489,7 +18562,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" s="26" t="s">
         <v>89</v>
       </c>
@@ -18497,7 +18570,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" s="26" t="s">
         <v>82</v>
       </c>
@@ -18505,7 +18578,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" s="26" t="s">
         <v>79</v>
       </c>
@@ -18513,7 +18586,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" s="26" t="s">
         <v>83</v>
       </c>
@@ -18521,7 +18594,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
         <v>118</v>
       </c>
@@ -18529,7 +18602,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
         <v>80</v>
       </c>
@@ -18537,7 +18610,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>75</v>
       </c>
@@ -18545,7 +18618,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="26" t="s">
         <v>90</v>
       </c>
@@ -18553,7 +18626,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="26" t="s">
         <v>156</v>
       </c>
@@ -18561,7 +18634,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
         <v>154</v>
       </c>
@@ -18578,13 +18651,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF17EB8-02F1-485E-9D81-51CF2F0BE0EA}">
   <dimension ref="A1:K44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" s="36">
         <v>1</v>
       </c>
@@ -18616,7 +18689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -18651,7 +18724,7 @@
         <v>2178000000</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>148</v>
       </c>
@@ -18686,7 +18759,7 @@
         <v>456000000</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>144</v>
       </c>
@@ -18721,7 +18794,7 @@
         <v>158400000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>150</v>
       </c>
@@ -18756,7 +18829,7 @@
         <v>123300000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>152</v>
       </c>
@@ -18791,7 +18864,7 @@
         <v>1169600000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -18826,7 +18899,7 @@
         <v>19900000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -18861,7 +18934,7 @@
         <v>254000000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>141</v>
       </c>
@@ -18896,7 +18969,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>142</v>
       </c>
@@ -18931,7 +19004,7 @@
         <v>41300000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>143</v>
       </c>
@@ -18966,7 +19039,7 @@
         <v>13300000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>145</v>
       </c>
@@ -19001,7 +19074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>146</v>
       </c>
@@ -19036,7 +19109,7 @@
         <v>8200000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>147</v>
       </c>
@@ -19071,7 +19144,7 @@
         <v>1399100000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>149</v>
       </c>
@@ -19106,7 +19179,7 @@
         <v>21500000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>156</v>
       </c>
@@ -19141,7 +19214,7 @@
         <v>79000000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>151</v>
       </c>
@@ -19176,7 +19249,7 @@
         <v>1282000000</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>153</v>
       </c>
@@ -19211,7 +19284,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
@@ -19223,7 +19296,7 @@
       <c r="J19" s="25"/>
       <c r="K19" s="25"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" s="37"/>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -19235,7 +19308,7 @@
       <c r="J20" s="37"/>
       <c r="K20" s="37"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
@@ -19247,7 +19320,7 @@
       <c r="J21" s="42"/>
       <c r="K21" s="42"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -19259,7 +19332,7 @@
       <c r="J22" s="42"/>
       <c r="K22" s="42"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23" s="37"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -19271,7 +19344,7 @@
       <c r="J23" s="25"/>
       <c r="K23" s="25"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
@@ -19283,7 +19356,7 @@
       <c r="J24" s="25"/>
       <c r="K24" s="25"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -19295,7 +19368,7 @@
       <c r="J25" s="25"/>
       <c r="K25" s="25"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
@@ -19307,7 +19380,7 @@
       <c r="J26" s="25"/>
       <c r="K26" s="25"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
@@ -19319,7 +19392,7 @@
       <c r="J27" s="25"/>
       <c r="K27" s="25"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -19331,7 +19404,7 @@
       <c r="J28" s="25"/>
       <c r="K28" s="25"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -19343,7 +19416,7 @@
       <c r="J29" s="25"/>
       <c r="K29" s="25"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -19355,7 +19428,7 @@
       <c r="J30" s="25"/>
       <c r="K30" s="25"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -19367,7 +19440,7 @@
       <c r="J31" s="25"/>
       <c r="K31" s="25"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -19379,7 +19452,7 @@
       <c r="J32" s="25"/>
       <c r="K32" s="25"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -19391,7 +19464,7 @@
       <c r="J33" s="25"/>
       <c r="K33" s="25"/>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
@@ -19403,7 +19476,7 @@
       <c r="J34" s="25"/>
       <c r="K34" s="25"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -19415,7 +19488,7 @@
       <c r="J35" s="25"/>
       <c r="K35" s="25"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
@@ -19427,7 +19500,7 @@
       <c r="J36" s="25"/>
       <c r="K36" s="25"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
@@ -19439,7 +19512,7 @@
       <c r="J37" s="25"/>
       <c r="K37" s="25"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
@@ -19451,7 +19524,7 @@
       <c r="J38" s="25"/>
       <c r="K38" s="25"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -19463,7 +19536,7 @@
       <c r="J39" s="25"/>
       <c r="K39" s="25"/>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="25"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
@@ -19475,7 +19548,7 @@
       <c r="J40" s="25"/>
       <c r="K40" s="25"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -19487,7 +19560,7 @@
       <c r="J41" s="25"/>
       <c r="K41" s="25"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="25"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -19499,7 +19572,7 @@
       <c r="J42" s="25"/>
       <c r="K42" s="25"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -19511,7 +19584,7 @@
       <c r="J43" s="25"/>
       <c r="K43" s="25"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="25"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
